--- a/reports/pdf_rolling5_20260702.xlsx
+++ b/reports/pdf_rolling5_20260702.xlsx
@@ -739,21 +739,21 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3311178200</v>
+        <v>589152520</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.573</v>
+        <v>0.102</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>102→133</t>
+          <t>77→108</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -779,21 +779,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>589152520</v>
+        <v>3311178200</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.102</v>
+        <v>0.573</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>77→108</t>
+          <t>102→133</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -939,21 +939,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1820357000</v>
+        <v>2652727000</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.315</v>
+        <v>0.459</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>30→37</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -979,21 +979,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2652727000</v>
+        <v>1820357000</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.459</v>
+        <v>0.315</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>30→37</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G14" s="17" t="n"/>
@@ -1005,21 +1005,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1173796800</v>
+        <v>504385200</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.203</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1031,21 +1031,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>504385200</v>
+        <v>816446400</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>37→43</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1057,21 +1057,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>816446400</v>
+        <v>1173796800</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.141</v>
+        <v>0.203</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>37→43</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -2322,21 +2322,21 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코오롱티슈진</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-49296000</v>
+        <v>-22183200</v>
       </c>
       <c r="J57" s="16" t="n">
-        <v>-0.131</v>
+        <v>-0.059</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>68→65</t>
+          <t>80→77</t>
         </is>
       </c>
     </row>
@@ -2348,21 +2348,21 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>코오롱티슈진</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-22183200</v>
+        <v>-49296000</v>
       </c>
       <c r="J58" s="16" t="n">
-        <v>-0.059</v>
+        <v>-0.131</v>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>80→77</t>
+          <t>68→65</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260702.xlsx
+++ b/reports/pdf_rolling5_20260702.xlsx
@@ -570,7 +570,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,782억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 12종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 6,036억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 12종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -666,10 +666,10 @@
         <v>59</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2800175400</v>
+        <v>2819132100</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.484</v>
+        <v>0.467</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         <v>-97</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-695065140</v>
+        <v>-699770610</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.12</v>
+        <v>-0.116</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         <v>33</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1750458600</v>
+        <v>1762308900</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.303</v>
+        <v>0.292</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>-74</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-6320221600</v>
+        <v>-6363008400</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-1.093</v>
+        <v>-1.054</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -739,21 +739,21 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>589152520</v>
+        <v>3333594300</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.102</v>
+        <v>0.552</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>77→108</t>
+          <t>102→133</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -765,10 +765,10 @@
         <v>-47</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-5472134800</v>
+        <v>-5509180200</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.946</v>
+        <v>-0.913</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -779,21 +779,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3311178200</v>
+        <v>593140980</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.573</v>
+        <v>0.098</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>102→133</t>
+          <t>77→108</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -805,10 +805,10 @@
         <v>-39</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1721920200</v>
+        <v>-1733577300</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.298</v>
+        <v>-0.287</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1273888000</v>
+        <v>1282512000</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.22</v>
+        <v>0.212</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-490984560</v>
+        <v>-494308440</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.082</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2568456000</v>
+        <v>2585844000</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.444</v>
+        <v>0.428</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>-24</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2307888000</v>
+        <v>-2323512000</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-0.399</v>
+        <v>-0.385</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1721610000</v>
+        <v>1733265000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.298</v>
+        <v>0.287</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         <v>-20</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2744236000</v>
+        <v>-2762814000</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-0.475</v>
+        <v>-0.458</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -939,21 +939,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2652727000</v>
+        <v>1832680500</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.459</v>
+        <v>0.304</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>30→37</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -965,10 +965,10 @@
         <v>-19</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2115874200</v>
+        <v>-2130198300</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-0.366</v>
+        <v>-0.353</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -979,21 +979,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1820357000</v>
+        <v>2670685500</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.315</v>
+        <v>0.442</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>30→37</t>
         </is>
       </c>
       <c r="G14" s="17" t="n"/>
@@ -1005,21 +1005,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>504385200</v>
+        <v>1181743200</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.196</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1038,10 +1038,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>816446400</v>
+        <v>821973600</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.141</v>
+        <v>0.136</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
@@ -1057,21 +1057,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1173796800</v>
+        <v>507799800</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.203</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -1083,7 +1083,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,784억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 3종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,954억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1179,10 +1179,10 @@
         <v>493</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>12277672000</v>
+        <v>12321056000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>2.566</v>
+        <v>2.487</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         <v>-20</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1890440000</v>
+        <v>-1897120000</v>
       </c>
       <c r="J22" s="16" t="n">
-        <v>-0.395</v>
+        <v>-0.383</v>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
         <v>68</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>472247760</v>
+        <v>473916480</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1433112000</v>
+        <v>1438176000</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,651억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 6종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,774억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1360,10 +1360,10 @@
         <v>40</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1330560000</v>
+        <v>1342880000</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>0.364</v>
+        <v>0.356</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         <v>-149</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-5654728800</v>
+        <v>-5707087400</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>-1.549</v>
+        <v>-1.512</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>26</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>7036848000</v>
+        <v>7102004000</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>1.927</v>
+        <v>1.882</v>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         <v>-87</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-3709540800</v>
+        <v>-3743888400</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>-1.016</v>
+        <v>-0.992</v>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         <v>25</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1088640000</v>
+        <v>1098720000</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>0.298</v>
+        <v>0.291</v>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         <v>-60</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-4685688000</v>
+        <v>-4729074000</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>-1.283</v>
+        <v>-1.253</v>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
@@ -1480,10 +1480,10 @@
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1290718800</v>
+        <v>1302669900</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.353</v>
+        <v>0.345</v>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         <v>-7</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-80120880</v>
+        <v>-80862740</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>-0.022</v>
+        <v>-0.021</v>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         <v>21</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2651292000</v>
+        <v>2675841000</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.726</v>
+        <v>0.709</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         <v>19</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>3037986000</v>
+        <v>3066115500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.832</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,801억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,898억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1664,7 +1664,7 @@
         <v>2924680000</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>1.044</v>
+        <v>1.009</v>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>-341147500</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>-0.122</v>
+        <v>-0.118</v>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 376억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 14종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 394억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 14종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -1790,10 +1790,10 @@
         <v>110</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>124962200</v>
+        <v>131566600</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.332</v>
+        <v>0.334</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         <v>-111</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-204756150</v>
+        <v>-245970450</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-0.544</v>
+        <v>-0.624</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         <v>80</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>67497600</v>
+        <v>68572000</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
         <v>-87</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-269765250</v>
+        <v>-273889050</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.717</v>
+        <v>-0.695</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
@@ -1870,10 +1870,10 @@
         <v>78</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>323505000</v>
+        <v>347536800</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.859</v>
+        <v>0.881</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         <v>-50</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-79197500</v>
+        <v>-81765000</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.21</v>
+        <v>-0.207</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
         <v>29</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>107677000</v>
+        <v>111113500</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.286</v>
+        <v>0.282</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         <v>-40</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-128138000</v>
+        <v>-122134000</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.34</v>
+        <v>-0.31</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
         <v>27</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>47565900</v>
+        <v>48952350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-24619560</v>
+        <v>-72000600</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.065</v>
+        <v>-0.183</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1990,10 +1990,10 @@
         <v>26</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>105986400</v>
+        <v>113586200</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.282</v>
+        <v>0.288</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-72553600</v>
+        <v>-24442600</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.193</v>
+        <v>-0.062</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -2030,10 +2030,10 @@
         <v>23</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>105931100</v>
+        <v>102660500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.281</v>
+        <v>0.26</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
         <v>-17</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-62583800</v>
+        <v>-64464000</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-0.166</v>
+        <v>-0.163</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
         <v>17</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>39819950</v>
+        <v>41095800</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>-15</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-37505250</v>
+        <v>-42126750</v>
       </c>
       <c r="J51" s="16" t="n">
-        <v>-0.1</v>
+        <v>-0.107</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -2110,10 +2110,10 @@
         <v>15</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>199198500</v>
+        <v>196236000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.529</v>
+        <v>0.498</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         <v>-11</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-167021800</v>
+        <v>-164414800</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-0.444</v>
+        <v>-0.417</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
         <v>11</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>35194500</v>
+        <v>36106950</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         <v>-11</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-35629000</v>
+        <v>-38236000</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-0.095</v>
+        <v>-0.097</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
@@ -2190,10 +2190,10 @@
         <v>8</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>123935200</v>
+        <v>133668000</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>0.329</v>
+        <v>0.339</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
         <v>-9</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-176683500</v>
+        <v>-190192500</v>
       </c>
       <c r="J54" s="16" t="n">
-        <v>-0.469</v>
+        <v>-0.482</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         <v>7</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>51594900</v>
+        <v>53253900</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.137</v>
+        <v>0.135</v>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-113760000</v>
+        <v>-118381500</v>
       </c>
       <c r="J55" s="16" t="n">
-        <v>-0.302</v>
+        <v>-0.3</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         <v>4</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>115498000</v>
+        <v>106966000</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.307</v>
+        <v>0.271</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         <v>-4</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-46989200</v>
+        <v>-49706800</v>
       </c>
       <c r="J56" s="16" t="n">
-        <v>-0.125</v>
+        <v>-0.126</v>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         <v>4</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>114708000</v>
+        <v>115814000</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.305</v>
+        <v>0.294</v>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
@@ -2329,10 +2329,10 @@
         <v>-3</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-22183200</v>
+        <v>-22041000</v>
       </c>
       <c r="J57" s="16" t="n">
-        <v>-0.059</v>
+        <v>-0.056</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
         <v>-3</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-49296000</v>
+        <v>-50481000</v>
       </c>
       <c r="J58" s="16" t="n">
-        <v>-0.131</v>
+        <v>-0.128</v>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 613억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 5종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 639억      오늘 2026-07-02  vs  5일전 2026-06-25      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -2465,10 +2465,10 @@
         <v>184</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>906752000</v>
+        <v>898656000</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>1.48</v>
+        <v>1.407</v>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         <v>-622</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-888216000</v>
+        <v>-880285500</v>
       </c>
       <c r="J63" s="16" t="n">
-        <v>-1.45</v>
+        <v>-1.379</v>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
         <v>44</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>455347200</v>
+        <v>451281600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>0.743</v>
+        <v>0.707</v>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         <v>-214</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-536883200</v>
+        <v>-532089600</v>
       </c>
       <c r="J64" s="16" t="n">
-        <v>-0.876</v>
+        <v>-0.833</v>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         <v>32</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>1313536000</v>
+        <v>1301808000</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>2.144</v>
+        <v>2.039</v>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         <v>-136</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-618419200</v>
+        <v>-612897600</v>
       </c>
       <c r="J65" s="16" t="n">
-        <v>-1.009</v>
+        <v>-0.96</v>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
@@ -2585,10 +2585,10 @@
         <v>13</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>614432000</v>
+        <v>608946000</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>1.003</v>
+        <v>0.954</v>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
@@ -2604,10 +2604,10 @@
         <v>-17</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-681632000</v>
+        <v>-675546000</v>
       </c>
       <c r="J66" s="16" t="n">
-        <v>-1.112</v>
+        <v>-1.058</v>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
         <v>9</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>183153600</v>
+        <v>181518300</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.299</v>
+        <v>0.284</v>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260702.xlsx
+++ b/reports/pdf_rolling5_20260702.xlsx
@@ -739,21 +739,21 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3333594300</v>
+        <v>593140980</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.552</v>
+        <v>0.098</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>102→133</t>
+          <t>77→108</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -779,21 +779,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>593140980</v>
+        <v>3333594300</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.098</v>
+        <v>0.552</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>77→108</t>
+          <t>102→133</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -939,21 +939,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1832680500</v>
+        <v>2670685500</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.304</v>
+        <v>0.442</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>30→37</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -979,21 +979,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2670685500</v>
+        <v>1832680500</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.442</v>
+        <v>0.304</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>30→37</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G14" s="17" t="n"/>
@@ -1005,21 +1005,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1181743200</v>
+        <v>821973600</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.196</v>
+        <v>0.136</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>37→43</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1031,21 +1031,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>821973600</v>
+        <v>507799800</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.136</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>37→43</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1057,21 +1057,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>507799800</v>
+        <v>1181743200</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -2122,21 +2122,21 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>알지노믹스  (편출)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-164414800</v>
+        <v>-38236000</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-0.417</v>
+        <v>-0.097</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>47→36</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -2162,21 +2162,21 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-38236000</v>
+        <v>-164414800</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-0.097</v>
+        <v>-0.417</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>47→36</t>
         </is>
       </c>
     </row>
@@ -2202,21 +2202,21 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-190192500</v>
+        <v>-118381500</v>
       </c>
       <c r="J54" s="16" t="n">
-        <v>-0.482</v>
+        <v>-0.3</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
@@ -2242,42 +2242,42 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-118381500</v>
+        <v>-190192500</v>
       </c>
       <c r="J55" s="16" t="n">
-        <v>-0.3</v>
+        <v>-0.482</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>파마리서치  (신규)</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>106966000</v>
+        <v>115814000</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.271</v>
+        <v>0.294</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>0→4</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2303,21 +2303,21 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>115814000</v>
+        <v>106966000</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.294</v>
+        <v>0.271</v>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>0→4</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260702.xlsx
+++ b/reports/pdf_rolling5_20260702.xlsx
@@ -939,21 +939,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2670685500</v>
+        <v>1832680500</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.442</v>
+        <v>0.304</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>30→37</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -979,21 +979,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1832680500</v>
+        <v>2670685500</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.304</v>
+        <v>0.442</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>30→37</t>
         </is>
       </c>
       <c r="G14" s="17" t="n"/>
@@ -1005,21 +1005,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>821973600</v>
+        <v>507799800</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.136</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>37→43</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1031,21 +1031,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>507799800</v>
+        <v>821973600</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>37→43</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1473,21 +1473,21 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1302669900</v>
+        <v>2675841000</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.345</v>
+        <v>0.709</v>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>99→120</t>
+          <t>19→40</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -1513,21 +1513,21 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2675841000</v>
+        <v>1302669900</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.709</v>
+        <v>0.345</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>19→40</t>
+          <t>99→120</t>
         </is>
       </c>
       <c r="G33" s="17" t="n"/>
@@ -2202,21 +2202,21 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-118381500</v>
+        <v>-190192500</v>
       </c>
       <c r="J54" s="16" t="n">
-        <v>-0.3</v>
+        <v>-0.482</v>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>41→32</t>
         </is>
       </c>
     </row>
@@ -2242,21 +2242,21 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-190192500</v>
+        <v>-118381500</v>
       </c>
       <c r="J55" s="16" t="n">
-        <v>-0.482</v>
+        <v>-0.3</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>41→32</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260702.xlsx
+++ b/reports/pdf_rolling5_20260702.xlsx
@@ -939,21 +939,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1832680500</v>
+        <v>2670685500</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.304</v>
+        <v>0.442</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>38→45</t>
+          <t>30→37</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -979,21 +979,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>2670685500</v>
+        <v>1832680500</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.442</v>
+        <v>0.304</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>30→37</t>
+          <t>38→45</t>
         </is>
       </c>
       <c r="G14" s="17" t="n"/>
@@ -1005,21 +1005,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>507799800</v>
+        <v>821973600</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>37→43</t>
         </is>
       </c>
       <c r="G15" s="17" t="n"/>
@@ -1031,21 +1031,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>821973600</v>
+        <v>1181743200</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.136</v>
+        <v>0.196</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>37→43</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1057,21 +1057,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1181743200</v>
+        <v>507799800</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.196</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -1473,21 +1473,21 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>2675841000</v>
+        <v>1302669900</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.709</v>
+        <v>0.345</v>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>19→40</t>
+          <t>99→120</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -1513,21 +1513,21 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>1302669900</v>
+        <v>2675841000</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.345</v>
+        <v>0.709</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>99→120</t>
+          <t>19→40</t>
         </is>
       </c>
       <c r="G33" s="17" t="n"/>
@@ -1962,21 +1962,21 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-72000600</v>
+        <v>-24442600</v>
       </c>
       <c r="J48" s="16" t="n">
-        <v>-0.183</v>
+        <v>-0.062</v>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -2002,21 +2002,21 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-24442600</v>
+        <v>-72000600</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.062</v>
+        <v>-0.183</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -2122,21 +2122,21 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-38236000</v>
+        <v>-164414800</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-0.097</v>
+        <v>-0.417</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>47→36</t>
         </is>
       </c>
     </row>
@@ -2162,21 +2162,21 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>알지노믹스  (편출)</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-164414800</v>
+        <v>-38236000</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-0.417</v>
+        <v>-0.097</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>47→36</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -2263,21 +2263,21 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>115814000</v>
+        <v>106966000</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>0.294</v>
+        <v>0.271</v>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>0→4</t>
+          <t>22→26</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -2303,40 +2303,40 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>파마리서치  (신규)</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>106966000</v>
+        <v>115814000</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>0.271</v>
+        <v>0.294</v>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
+          <t>0→4</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>코오롱티슈진</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-22041000</v>
+        <v>-50481000</v>
       </c>
       <c r="J57" s="16" t="n">
-        <v>-0.056</v>
+        <v>-0.128</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>80→77</t>
+          <t>68→65</t>
         </is>
       </c>
     </row>
@@ -2348,21 +2348,21 @@
       <c r="E58" s="17" t="n"/>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>코오롱티슈진</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-50481000</v>
+        <v>-22041000</v>
       </c>
       <c r="J58" s="16" t="n">
-        <v>-0.128</v>
+        <v>-0.056</v>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>68→65</t>
+          <t>80→77</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260702.xlsx
+++ b/reports/pdf_rolling5_20260702.xlsx
@@ -739,21 +739,21 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>593140980</v>
+        <v>3333594300</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.098</v>
+        <v>0.552</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>77→108</t>
+          <t>102→133</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -779,21 +779,21 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3333594300</v>
+        <v>593140980</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.552</v>
+        <v>0.098</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>102→133</t>
+          <t>77→108</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1031,21 +1031,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1181743200</v>
+        <v>507799800</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.196</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>36→42</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1057,21 +1057,21 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>507799800</v>
+        <v>1181743200</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>36→42</t>
         </is>
       </c>
       <c r="G17" s="17" t="n"/>
@@ -1473,21 +1473,21 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1302669900</v>
+        <v>2675841000</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.345</v>
+        <v>0.709</v>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>99→120</t>
+          <t>19→40</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -1513,21 +1513,21 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>2675841000</v>
+        <v>1302669900</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.709</v>
+        <v>0.345</v>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>19→40</t>
+          <t>99→120</t>
         </is>
       </c>
       <c r="G33" s="17" t="n"/>
@@ -2122,21 +2122,21 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>알지노믹스  (편출)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-164414800</v>
+        <v>-38236000</v>
       </c>
       <c r="J52" s="16" t="n">
-        <v>-0.417</v>
+        <v>-0.097</v>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>47→36</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -2162,21 +2162,21 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스  (편출)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-38236000</v>
+        <v>-164414800</v>
       </c>
       <c r="J53" s="16" t="n">
-        <v>-0.097</v>
+        <v>-0.417</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>47→36</t>
         </is>
       </c>
     </row>
